--- a/artfynd/A 30125-2023 artfynd.xlsx
+++ b/artfynd/A 30125-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30125-2023 artfynd.xlsx
+++ b/artfynd/A 30125-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121175086</v>
       </c>
       <c r="B3" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30125-2023 artfynd.xlsx
+++ b/artfynd/A 30125-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121175086</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30125-2023 artfynd.xlsx
+++ b/artfynd/A 30125-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121175086</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 30125-2023 artfynd.xlsx
+++ b/artfynd/A 30125-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121175086</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
